--- a/outputs/monitor_xlsx/20260402.xlsx
+++ b/outputs/monitor_xlsx/20260402.xlsx
@@ -544,10 +544,6 @@
           <t>-1.82%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.02%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-0.21%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-2.75%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.19%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+0.40%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-2.73%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+11.41%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-386.96億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-392.96億</t>
@@ -807,7 +769,6 @@
           <t>84.24億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>49.57億</t>
@@ -818,8 +779,6 @@
           <t>247.85億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>140.76%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>128.65%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-372.6億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>8901口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8568口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>0.09億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>8.05億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1940,112 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6605</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>435</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G16" t="n">
+        <v>210</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-144</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-330</v>
+      </c>
+      <c r="J16" t="n">
+        <v>23</v>
+      </c>
+      <c r="K16" t="n">
+        <v>356</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1534</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-8988</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-4.73</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1535</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5962</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-424</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H17" t="n">
+        <v>289</v>
+      </c>
+      <c r="I17" t="n">
+        <v>540</v>
+      </c>
+      <c r="J17" t="n">
+        <v>120</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L17" t="n">
+        <v>11851</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-106310</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260402.xlsx
+++ b/outputs/monitor_xlsx/20260402.xlsx
@@ -544,6 +544,10 @@
           <t>-1.82%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,6 +570,10 @@
           <t>-1.02%</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +591,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,6 +618,10 @@
           <t>-0.21%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -627,6 +644,10 @@
           <t>-2.75%</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +670,10 @@
           <t>+0.19%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -671,6 +696,10 @@
           <t>+0.40%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +722,10 @@
           <t>-2.73%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -715,6 +748,10 @@
           <t>+11.41%</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -729,17 +766,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-386.96億</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-392.96億</t>
+          <t>-397.19億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1964.82億</t>
+          <t>-1985.97億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -766,19 +804,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>84.24億</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.57億</t>
+          <t>50.11億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>247.85億</t>
-        </is>
-      </c>
+          <t>250.53億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -793,14 +834,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>140.76%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>128.65%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -815,9 +860,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-372.6億</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,11 +885,15 @@
           <t>8901口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8568口</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,6 +911,7 @@
           <t>0.09億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>8.05億</t>
@@ -869,12 +924,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-7.94億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-158.74億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -921,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-392.96億</t>
+          <t>-397.19億</t>
         </is>
       </c>
     </row>
@@ -933,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1964.82億</t>
+          <t>-1985.97億</t>
         </is>
       </c>
     </row>
@@ -961,6 +1016,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -969,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>49.57億</t>
+          <t>50.11億</t>
         </is>
       </c>
     </row>
@@ -981,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>247.85億</t>
+          <t>250.53億</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-7.94億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-158.74億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1100,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1284,12 +1336,7 @@
       <c r="N4" t="n">
         <v>-4624902</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1344,12 +1391,7 @@
       <c r="N5" t="n">
         <v>-78957</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1404,12 +1446,7 @@
       <c r="N6" t="n">
         <v>-649339</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1464,12 +1501,7 @@
       <c r="N7" t="n">
         <v>-6483124</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1478,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1492,44 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2785</v>
+        <v>1590</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-2.62</v>
+        <v>-4.22</v>
       </c>
       <c r="F8" t="n">
-        <v>4147</v>
+        <v>3328</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-20</v>
+        <v>-243</v>
       </c>
       <c r="H8" t="n">
-        <v>-935</v>
+        <v>-1541</v>
       </c>
       <c r="I8" t="n">
-        <v>177</v>
+        <v>394</v>
       </c>
       <c r="J8" t="n">
-        <v>380</v>
+        <v>1564</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="L8" t="n">
-        <v>1837</v>
+        <v>1843</v>
       </c>
       <c r="M8" t="n">
-        <v>7426</v>
+        <v>8685</v>
       </c>
       <c r="N8" t="n">
-        <v>-89568</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140279</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1538,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1552,44 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2000</v>
+        <v>1535</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-1.48</v>
+        <v>-4.66</v>
       </c>
       <c r="F9" t="n">
-        <v>3799</v>
+        <v>5962</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-89</v>
+        <v>-424</v>
       </c>
       <c r="H9" t="n">
-        <v>-585</v>
+        <v>306</v>
       </c>
       <c r="I9" t="n">
-        <v>152</v>
+        <v>289</v>
       </c>
       <c r="J9" t="n">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="L9" t="n">
-        <v>3795</v>
+        <v>2030</v>
       </c>
       <c r="M9" t="n">
-        <v>15831</v>
+        <v>9821</v>
       </c>
       <c r="N9" t="n">
-        <v>-19425</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106310</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1598,58 +1620,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1825</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>5.49</v>
+        <v>2785</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-2.62</v>
       </c>
       <c r="F10" t="n">
-        <v>4365</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>183</v>
+        <v>4147</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>-20</v>
       </c>
       <c r="H10" t="n">
-        <v>-196</v>
+        <v>-935</v>
       </c>
       <c r="I10" t="n">
-        <v>651</v>
+        <v>177</v>
       </c>
       <c r="J10" t="n">
-        <v>296</v>
+        <v>380</v>
       </c>
       <c r="K10" t="n">
-        <v>-56</v>
+        <v>153</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>1837</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>7426</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89568</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1658,55 +1675,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>384</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>2.26</v>
+        <v>2000</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-1.48</v>
       </c>
       <c r="F11" t="n">
-        <v>1295</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>218</v>
+        <v>3799</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>-89</v>
       </c>
       <c r="H11" t="n">
-        <v>-418</v>
+        <v>-585</v>
+      </c>
+      <c r="I11" t="n">
+        <v>152</v>
       </c>
       <c r="J11" t="n">
-        <v>-20</v>
+        <v>103</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="L11" t="n">
-        <v>-264</v>
+        <v>3795</v>
       </c>
       <c r="M11" t="n">
-        <v>-1363</v>
+        <v>15831</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19425</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1715,12 +1730,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1729,44 +1744,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1590</v>
+        <v>6605</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-4.22</v>
+        <v>-9.4</v>
       </c>
       <c r="F12" t="n">
-        <v>3328</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-243</v>
+        <v>435</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>63</v>
       </c>
       <c r="H12" t="n">
-        <v>-1541</v>
+        <v>148</v>
       </c>
       <c r="I12" t="n">
-        <v>394</v>
+        <v>-144</v>
       </c>
       <c r="J12" t="n">
-        <v>1564</v>
+        <v>-186</v>
       </c>
       <c r="K12" t="n">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="L12" t="n">
-        <v>1843</v>
+        <v>356</v>
       </c>
       <c r="M12" t="n">
-        <v>8685</v>
+        <v>1178</v>
       </c>
       <c r="N12" t="n">
-        <v>-140279</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8988</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1775,12 +1785,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1789,41 +1799,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>895</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.45</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>749</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>102</v>
+        <v>183</v>
       </c>
       <c r="H13" t="n">
-        <v>1361</v>
+        <v>-196</v>
+      </c>
+      <c r="I13" t="n">
+        <v>651</v>
       </c>
       <c r="J13" t="n">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="K13" t="n">
-        <v>-7</v>
+        <v>-56</v>
       </c>
       <c r="L13" t="n">
-        <v>-68</v>
+        <v>35</v>
       </c>
       <c r="M13" t="n">
-        <v>-504</v>
+        <v>41</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1832,55 +1840,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.95</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>6.21</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>44796</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>-2733</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>-5643</v>
+        <v>-418</v>
       </c>
       <c r="J14" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K14" t="n">
+        <v>30</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-264</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1363</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>44</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9515</v>
-      </c>
-      <c r="M14" t="n">
-        <v>34873</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-145073</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1889,55 +1892,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.95</v>
+        <v>974</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>9.960000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>53264</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-2097</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>102</v>
       </c>
       <c r="H15" t="n">
-        <v>2813</v>
+        <v>1361</v>
       </c>
       <c r="J15" t="n">
+        <v>346</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-68</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-504</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>106</v>
-      </c>
-      <c r="L15" t="n">
-        <v>12069</v>
-      </c>
-      <c r="M15" t="n">
-        <v>34912</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-97303</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1946,106 +1944,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6605</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>435</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="G16" t="n">
-        <v>210</v>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F16" t="n">
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>47</v>
       </c>
       <c r="H16" t="n">
-        <v>-144</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-330</v>
+        <v>-105</v>
       </c>
       <c r="J16" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>-6</v>
       </c>
       <c r="L16" t="n">
-        <v>1534</v>
+        <v>-5</v>
       </c>
       <c r="M16" t="n">
-        <v>-8988</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.73</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1535</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>-4.66</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5962</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>-424</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-117</v>
-      </c>
-      <c r="H17" t="n">
-        <v>289</v>
-      </c>
-      <c r="I17" t="n">
-        <v>540</v>
-      </c>
-      <c r="J17" t="n">
-        <v>120</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2030</v>
-      </c>
-      <c r="L17" t="n">
-        <v>11851</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-106310</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>偏空</t>
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260402.xlsx
+++ b/outputs/monitor_xlsx/20260402.xlsx
@@ -544,10 +544,6 @@
           <t>-1.82%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.02%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-0.21%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>-2.75%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.19%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+0.40%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-2.73%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+11.41%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-397.19億</t>
@@ -807,7 +769,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>50.11億</t>
@@ -818,8 +779,6 @@
           <t>250.53億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>128.65%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>8901口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8568口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>0.09億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>8.05億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1991,6 +1934,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12708</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>674</v>
+      </c>
+      <c r="G17" t="n">
+        <v>770</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1578</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2366</v>
+      </c>
+      <c r="J17" t="n">
+        <v>203</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8476</v>
+      </c>
+      <c r="L17" t="n">
+        <v>32042</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21734</v>
+      </c>
+      <c r="N17" t="n">
+        <v>29.32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260402.xlsx
+++ b/outputs/monitor_xlsx/20260402.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1259,13 +1258,13 @@
         <v>-44024</v>
       </c>
       <c r="H4" t="n">
-        <v>-229766</v>
+        <v>-273790</v>
       </c>
       <c r="I4" t="n">
         <v>3000</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="K4" t="n">
         <v>19011</v>
@@ -1274,11 +1273,14 @@
         <v>13337</v>
       </c>
       <c r="M4" t="n">
-        <v>56517</v>
+        <v>69854</v>
       </c>
       <c r="N4" t="n">
         <v>-4624902</v>
       </c>
+      <c r="O4" t="n">
+        <v>-2.03</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1314,13 +1316,13 @@
         <v>-104</v>
       </c>
       <c r="H5" t="n">
-        <v>2025</v>
+        <v>1921</v>
       </c>
       <c r="I5" t="n">
         <v>-82</v>
       </c>
       <c r="J5" t="n">
-        <v>-1598</v>
+        <v>-1680</v>
       </c>
       <c r="K5" t="n">
         <v>58</v>
@@ -1329,11 +1331,14 @@
         <v>2691</v>
       </c>
       <c r="M5" t="n">
-        <v>11001</v>
+        <v>13692</v>
       </c>
       <c r="N5" t="n">
         <v>-78957</v>
       </c>
+      <c r="O5" t="n">
+        <v>-10.28</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1369,13 +1374,13 @@
         <v>-2172</v>
       </c>
       <c r="H6" t="n">
-        <v>-8301</v>
+        <v>-10473</v>
       </c>
       <c r="I6" t="n">
         <v>96</v>
       </c>
       <c r="J6" t="n">
-        <v>1116</v>
+        <v>1212</v>
       </c>
       <c r="K6" t="n">
         <v>252</v>
@@ -1384,11 +1389,14 @@
         <v>5368</v>
       </c>
       <c r="M6" t="n">
-        <v>22104</v>
+        <v>27472</v>
       </c>
       <c r="N6" t="n">
         <v>-649339</v>
       </c>
+      <c r="O6" t="n">
+        <v>0.88</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1424,13 +1432,13 @@
         <v>-9386</v>
       </c>
       <c r="H7" t="n">
-        <v>-41352</v>
+        <v>-50738</v>
       </c>
       <c r="I7" t="n">
         <v>-193</v>
       </c>
       <c r="J7" t="n">
-        <v>2993</v>
+        <v>2801</v>
       </c>
       <c r="K7" t="n">
         <v>468</v>
@@ -1439,11 +1447,14 @@
         <v>26598</v>
       </c>
       <c r="M7" t="n">
-        <v>106041</v>
+        <v>132639</v>
       </c>
       <c r="N7" t="n">
         <v>-6483124</v>
       </c>
+      <c r="O7" t="n">
+        <v>-1.84</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1479,13 +1490,13 @@
         <v>-243</v>
       </c>
       <c r="H8" t="n">
-        <v>-1541</v>
+        <v>-1784</v>
       </c>
       <c r="I8" t="n">
         <v>394</v>
       </c>
       <c r="J8" t="n">
-        <v>1564</v>
+        <v>1959</v>
       </c>
       <c r="K8" t="n">
         <v>173</v>
@@ -1494,11 +1505,14 @@
         <v>1843</v>
       </c>
       <c r="M8" t="n">
-        <v>8685</v>
+        <v>10528</v>
       </c>
       <c r="N8" t="n">
         <v>-140279</v>
       </c>
+      <c r="O8" t="n">
+        <v>3.1</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1534,13 +1548,13 @@
         <v>-424</v>
       </c>
       <c r="H9" t="n">
-        <v>306</v>
+        <v>-117</v>
       </c>
       <c r="I9" t="n">
         <v>289</v>
       </c>
       <c r="J9" t="n">
-        <v>252</v>
+        <v>540</v>
       </c>
       <c r="K9" t="n">
         <v>120</v>
@@ -1549,11 +1563,14 @@
         <v>2030</v>
       </c>
       <c r="M9" t="n">
-        <v>9821</v>
+        <v>11851</v>
       </c>
       <c r="N9" t="n">
         <v>-106310</v>
       </c>
+      <c r="O9" t="n">
+        <v>1.4</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1589,13 +1606,13 @@
         <v>-20</v>
       </c>
       <c r="H10" t="n">
-        <v>-935</v>
+        <v>-955</v>
       </c>
       <c r="I10" t="n">
         <v>177</v>
       </c>
       <c r="J10" t="n">
-        <v>380</v>
+        <v>557</v>
       </c>
       <c r="K10" t="n">
         <v>153</v>
@@ -1604,11 +1621,14 @@
         <v>1837</v>
       </c>
       <c r="M10" t="n">
-        <v>7426</v>
+        <v>9263</v>
       </c>
       <c r="N10" t="n">
         <v>-89568</v>
       </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1644,13 +1664,13 @@
         <v>-89</v>
       </c>
       <c r="H11" t="n">
-        <v>-585</v>
+        <v>-674</v>
       </c>
       <c r="I11" t="n">
         <v>152</v>
       </c>
       <c r="J11" t="n">
-        <v>103</v>
+        <v>255</v>
       </c>
       <c r="K11" t="n">
         <v>80</v>
@@ -1659,11 +1679,14 @@
         <v>3795</v>
       </c>
       <c r="M11" t="n">
-        <v>15831</v>
+        <v>19626</v>
       </c>
       <c r="N11" t="n">
         <v>-19425</v>
       </c>
+      <c r="O11" t="n">
+        <v>5.57</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1699,13 +1722,13 @@
         <v>63</v>
       </c>
       <c r="H12" t="n">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="I12" t="n">
         <v>-144</v>
       </c>
       <c r="J12" t="n">
-        <v>-186</v>
+        <v>-330</v>
       </c>
       <c r="K12" t="n">
         <v>23</v>
@@ -1714,11 +1737,14 @@
         <v>356</v>
       </c>
       <c r="M12" t="n">
-        <v>1178</v>
+        <v>1534</v>
       </c>
       <c r="N12" t="n">
         <v>-8988</v>
       </c>
+      <c r="O12" t="n">
+        <v>-4.73</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1742,25 +1768,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2315</v>
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
+        <v>2.16</v>
       </c>
       <c r="F13" t="n">
-        <v>2730</v>
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>183</v>
       </c>
       <c r="H13" t="n">
-        <v>-196</v>
+        <v>-12</v>
       </c>
       <c r="I13" t="n">
         <v>651</v>
       </c>
       <c r="J13" t="n">
-        <v>296</v>
+        <v>946</v>
       </c>
       <c r="K13" t="n">
         <v>-56</v>
@@ -1769,11 +1795,14 @@
         <v>35</v>
       </c>
       <c r="M13" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1797,19 +1826,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>449.5</v>
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
+        <v>9.94</v>
       </c>
       <c r="F14" t="n">
-        <v>3871</v>
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>-418</v>
+        <v>-200</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>-20</v>
@@ -1821,11 +1853,14 @@
         <v>-264</v>
       </c>
       <c r="M14" t="n">
-        <v>-1363</v>
+        <v>-1627</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1849,19 +1884,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F15" t="n">
-        <v>1350</v>
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>102</v>
       </c>
       <c r="H15" t="n">
-        <v>1361</v>
+        <v>1463</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>346</v>
@@ -1873,11 +1911,14 @@
         <v>-68</v>
       </c>
       <c r="M15" t="n">
-        <v>-504</v>
+        <v>-572</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1901,19 +1942,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F16" t="n">
-        <v>904</v>
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>47</v>
       </c>
       <c r="H16" t="n">
-        <v>-105</v>
+        <v>-59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>118</v>
@@ -1925,11 +1969,14 @@
         <v>-5</v>
       </c>
       <c r="M16" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1947,41 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>445.5</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>12708</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>674</v>
       </c>
-      <c r="G17" t="n">
-        <v>770</v>
-      </c>
       <c r="H17" t="n">
+        <v>208</v>
+      </c>
+      <c r="I17" t="n">
         <v>1578</v>
       </c>
-      <c r="I17" t="n">
-        <v>2366</v>
-      </c>
       <c r="J17" t="n">
+        <v>2698</v>
+      </c>
+      <c r="K17" t="n">
         <v>203</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8476</v>
       </c>
-      <c r="L17" t="n">
-        <v>32042</v>
-      </c>
       <c r="M17" t="n">
+        <v>39811</v>
+      </c>
+      <c r="N17" t="n">
         <v>-21734</v>
       </c>
-      <c r="N17" t="n">
-        <v>29.32</v>
+      <c r="O17" t="n">
+        <v>26.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260402.xlsx
+++ b/outputs/monitor_xlsx/20260402.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>26.91</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9301</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>-824</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4762</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-27</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1635</v>
+      </c>
+      <c r="K18" t="n">
+        <v>365</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6373</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31262</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400967</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-11.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>519</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>49200</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-1303</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-4393</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3016</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2490</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2839</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34088</v>
+      </c>
+      <c r="M19" t="n">
+        <v>157190</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393774</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>568</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="F20" t="n">
+        <v>46908</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>2130</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1144</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3489</v>
+      </c>
+      <c r="K20" t="n">
+        <v>933</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8201</v>
+      </c>
+      <c r="M20" t="n">
+        <v>42776</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161065</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
